--- a/StatPub/AltMetric.xlsx
+++ b/StatPub/AltMetric.xlsx
@@ -1,21 +1,212 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremycarlot/Documents/Website/JayCrlt.github.io/StatPub/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DAFC9A-50B5-0E47-AF63-FE77B6CBAA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="24300" windowHeight="15040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+  <si>
+    <t>doi</t>
+  </si>
+  <si>
+    <t>pubid</t>
+  </si>
+  <si>
+    <t>altid</t>
+  </si>
+  <si>
+    <t>AltmetricScore</t>
+  </si>
+  <si>
+    <t>10.26028/cybium/2017-413-003</t>
+  </si>
+  <si>
+    <t>u-x6o8ySG0sC</t>
+  </si>
+  <si>
+    <t>10.3390/jmse6010024</t>
+  </si>
+  <si>
+    <t>u5HHmVD_uO8C</t>
+  </si>
+  <si>
+    <t>90861092</t>
+  </si>
+  <si>
+    <t>10.1007/s00338-020-01916-8</t>
+  </si>
+  <si>
+    <t>9yKSN-GCB0IC</t>
+  </si>
+  <si>
+    <t>77314046</t>
+  </si>
+  <si>
+    <t>10.1371/journal.pbio.3000702</t>
+  </si>
+  <si>
+    <t>qjMakFHDy7sC</t>
+  </si>
+  <si>
+    <t>96796121</t>
+  </si>
+  <si>
+    <t>10.1038/s41597-020-00711-y</t>
+  </si>
+  <si>
+    <t>2osOgNQ5qMEC</t>
+  </si>
+  <si>
+    <t>93205299</t>
+  </si>
+  <si>
+    <t>10.1111/gcb.15610</t>
+  </si>
+  <si>
+    <t>UeHWp8X0CEIC</t>
+  </si>
+  <si>
+    <t>102574363</t>
+  </si>
+  <si>
+    <t>10.1002/ece3.8613</t>
+  </si>
+  <si>
+    <t>IjCSPb-OGe4C</t>
+  </si>
+  <si>
+    <t>125050022</t>
+  </si>
+  <si>
+    <t>10.1111/ddi.13549</t>
+  </si>
+  <si>
+    <t>zYLM7Y9cAGgC</t>
+  </si>
+  <si>
+    <t>129013899</t>
+  </si>
+  <si>
+    <t>10.1016/j.scitotenv.2022.157049</t>
+  </si>
+  <si>
+    <t>Tyk-4Ss8FVUC</t>
+  </si>
+  <si>
+    <t>130854736</t>
+  </si>
+  <si>
+    <t>10.1016/j.ecolind.2023.109952</t>
+  </si>
+  <si>
+    <t>YsMSGLbcyi4C</t>
+  </si>
+  <si>
+    <t>142625778</t>
+  </si>
+  <si>
+    <t>10.1038/s43247-023-00766-w</t>
+  </si>
+  <si>
+    <t>eQOLeE2rZwMC</t>
+  </si>
+  <si>
+    <t>145131808</t>
+  </si>
+  <si>
+    <t>10.1038/s41598-023-28945-x</t>
+  </si>
+  <si>
+    <t>Y0pCki6q_DkC</t>
+  </si>
+  <si>
+    <t>141934419</t>
+  </si>
+  <si>
+    <t>10.1111/gcb.17105</t>
+  </si>
+  <si>
+    <t>_FxGoFyzp5QC</t>
+  </si>
+  <si>
+    <t>158391407</t>
+  </si>
+  <si>
+    <t>10.1016/j.ecss.2024.108734</t>
+  </si>
+  <si>
+    <t>LkGwnXOMwfcC</t>
+  </si>
+  <si>
+    <t>170240233</t>
+  </si>
+  <si>
+    <t>10.1007/s00338-024-02544-2</t>
+  </si>
+  <si>
+    <t>UebtZRa9Y70C</t>
+  </si>
+  <si>
+    <t>166701640</t>
+  </si>
+  <si>
+    <t>10.1111/geb.13926</t>
+  </si>
+  <si>
+    <t>0EnyYjriUFMC</t>
+  </si>
+  <si>
+    <t>169435683</t>
+  </si>
+  <si>
+    <t>10.1038/s41467-025-55949-0</t>
+  </si>
+  <si>
+    <t>5nxA0vEk-isC</t>
+  </si>
+  <si>
+    <t>174135131</t>
+  </si>
+  <si>
+    <t>10.1007/s10021-025-00995-4</t>
+  </si>
+  <si>
+    <t>4TOpqqG69KYC</t>
+  </si>
+  <si>
+    <t>180489954</t>
+  </si>
+  <si>
+    <t>ULOm3_A8WrAC</t>
+  </si>
+  <si>
+    <t>Zph67rFs4hoC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.indic.2026.101255 </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +254,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +306,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +340,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +375,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,404 +551,291 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>doi</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>pubid</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>altid</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>AltmetricScore</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>10.26028/cybium/2017-413-003</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>u-x6o8ySG0sC</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>10.3390/jmse6010024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>u5HHmVD_uO8C</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>90861092</t>
-        </is>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>10.1007/s00338-020-01916-8</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>9yKSN-GCB0IC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>77314046</t>
-        </is>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
       <c r="D4">
         <v>13</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10.1371/journal.pbio.3000702</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>qjMakFHDy7sC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>96796121</t>
-        </is>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
       <c r="D5">
         <v>47</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10.1038/s41597-020-00711-y</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2osOgNQ5qMEC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>93205299</t>
-        </is>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>10.1111/gcb.15610</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>UeHWp8X0CEIC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>102574363</t>
-        </is>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
       </c>
       <c r="D7">
         <v>18</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>10.1002/ece3.8613</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>IjCSPb-OGe4C</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>125050022</t>
-        </is>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
       </c>
       <c r="D8">
         <v>8</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>10.1111/ddi.13549</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>zYLM7Y9cAGgC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>129013899</t>
-        </is>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
       </c>
       <c r="D9">
         <v>38</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>10.1016/j.scitotenv.2022.157049</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Tyk-4Ss8FVUC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>130854736</t>
-        </is>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
       </c>
       <c r="D10">
         <v>31</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10.1016/j.ecolind.2023.109952</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>YsMSGLbcyi4C</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>142625778</t>
-        </is>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
       </c>
       <c r="D11">
         <v>6</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10.1038/s43247-023-00766-w</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>eQOLeE2rZwMC</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>145131808</t>
-        </is>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
       </c>
       <c r="D12">
         <v>94</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>10.1038/s41598-023-28945-x</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Y0pCki6q_DkC</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>141934419</t>
-        </is>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
       </c>
       <c r="D13">
         <v>41</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>10.1111/gcb.17105</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>_FxGoFyzp5QC</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>158391407</t>
-        </is>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
       </c>
       <c r="D14">
         <v>37</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>10.1016/j.ecss.2024.108734</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LkGwnXOMwfcC</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>170240233</t>
-        </is>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>10.1007/s00338-024-02544-2</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>UebtZRa9Y70C</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>166701640</t>
-        </is>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
       </c>
       <c r="D16">
         <v>11</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>10.1111/geb.13926</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0EnyYjriUFMC</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>169435683</t>
-        </is>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
       </c>
       <c r="D17">
         <v>13</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>10.1038/s41467-025-55949-0</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5nxA0vEk-isC</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>174135131</t>
-        </is>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
       </c>
       <c r="D18">
         <v>99</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>10.1007/s10021-025-00995-4</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4TOpqqG69KYC</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>180489954</t>
-        </is>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ULOm3_A8WrAC</t>
-        </is>
-      </c>
-      <c r="D20">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Zph67rFs4hoC</t>
-        </is>
-      </c>
-      <c r="D21">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22">
         <v>0</v>
       </c>
     </row>

--- a/StatPub/AltMetric.xlsx
+++ b/StatPub/AltMetric.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremycarlot/Documents/Website/JayCrlt.github.io/StatPub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DAFC9A-50B5-0E47-AF63-FE77B6CBAA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25A66F2-4DBA-8C4A-97A0-383CE67D3E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="24300" windowHeight="15040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>doi</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.1016/j.indic.2026.101255 </t>
+  </si>
+  <si>
+    <t>4DMP91E08xMC</t>
   </si>
 </sst>
 </file>
@@ -822,6 +825,12 @@
       <c r="A20" t="s">
         <v>59</v>
       </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B21" t="s">

--- a/StatPub/AltMetric.xlsx
+++ b/StatPub/AltMetric.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremycarlot/Documents/Website/JayCrlt.github.io/StatPub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25A66F2-4DBA-8C4A-97A0-383CE67D3E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8907F35B-9BEE-D84A-8C71-81E0D556D18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="24300" windowHeight="15040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>doi</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>4DMP91E08xMC</t>
+  </si>
+  <si>
+    <t>10.1038/s43247-026-03631-8</t>
+  </si>
+  <si>
+    <t>QIV2ME_5wuYC</t>
   </si>
 </sst>
 </file>
@@ -246,11 +252,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -555,8 +562,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -579,6 +589,7 @@
       <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="2"/>
       <c r="D2">
         <v>0</v>
       </c>
@@ -590,7 +601,7 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D3">
@@ -604,7 +615,7 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4">
@@ -618,7 +629,7 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D5">
@@ -632,7 +643,7 @@
       <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6">
@@ -646,7 +657,7 @@
       <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D7">
@@ -660,7 +671,7 @@
       <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D8">
@@ -674,7 +685,7 @@
       <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D9">
@@ -688,7 +699,7 @@
       <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D10">
@@ -702,7 +713,7 @@
       <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D11">
@@ -716,7 +727,7 @@
       <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D12">
@@ -730,7 +741,7 @@
       <c r="B13" t="s">
         <v>37</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D13">
@@ -744,7 +755,7 @@
       <c r="B14" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D14">
@@ -758,7 +769,7 @@
       <c r="B15" t="s">
         <v>43</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D15">
@@ -772,7 +783,7 @@
       <c r="B16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D16">
@@ -786,7 +797,7 @@
       <c r="B17" t="s">
         <v>49</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D17">
@@ -800,7 +811,7 @@
       <c r="B18" t="s">
         <v>52</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D18">
@@ -814,7 +825,7 @@
       <c r="B19" t="s">
         <v>55</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D19">
@@ -828,23 +839,40 @@
       <c r="B20" t="s">
         <v>60</v>
       </c>
+      <c r="C20" s="2"/>
       <c r="D20">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>62</v>
+      </c>
+      <c r="C21" s="2">
+        <v>196770625</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
         <v>58</v>
       </c>
-      <c r="D22">
+      <c r="C23" s="2"/>
+      <c r="D23">
         <v>0</v>
       </c>
     </row>
